--- a/jogos_2025-06-11.xlsx
+++ b/jogos_2025-06-11.xlsx
@@ -643,22 +643,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="M2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T2" t="n">
         <v>3.3</v>
       </c>
-      <c r="N2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['87', '90+5', '13']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['45+1', '61']</t>
+          <t>['90+1', '5']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N3" t="n">
-        <v>5.32</v>
+        <v>4.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['90+1', '5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.37</v>
+        <v>7.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['87', '90+5', '13']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '61']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
         <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.09</v>
       </c>
-      <c r="X7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['45+1']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45819.85416666666</v>
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>3.5</v>
       </c>
       <c r="T8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.25</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45819.85416666666</v>
